--- a/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/mar-2026.xlsx
+++ b/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/mar-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC mar-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC mar-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3847,7 +3847,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -4518,7 +4518,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5738,7 +5738,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5982,7 +5982,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6897,7 +6897,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6958,7 +6958,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -7995,7 +7995,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -8483,7 +8483,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -8849,7 +8849,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -8971,7 +8971,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -10069,7 +10069,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -11472,7 +11472,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -11960,7 +11960,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -12143,7 +12143,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -12692,7 +12692,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -13058,7 +13058,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -13546,7 +13546,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -13790,7 +13790,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -13851,7 +13851,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -15559,7 +15559,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -16230,7 +16230,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -16291,7 +16291,7 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -16352,7 +16352,7 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">

--- a/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/mar-2026.xlsx
+++ b/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/mar-2026.xlsx
@@ -605,7 +605,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTA CORINA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE SEGURIDAD PÚBLICA</t>
+          <t>SUBSECRETARIA DE SEGURIDAD PUBLICA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Proyecto San Joaquín</t>
+          <t>ASOCIACIÓN DE MUNICIPIOS PARA LA SEGURIDAD COMUNITARIA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>PROGRAMA DE DESARROLLO LOGISTICO</t>
+          <t>SUBSECRETARIA DE TRANSPORTES</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SERVICIO HIDROGRAFICO Y OCEANOGRAFICO DE LA ARMADA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3350,7 +3350,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>DIRECCION DE INTELIGENCIA DE LA ARMADA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3842,7 +3842,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN CO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN COSTA</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3964,7 +3964,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL CLUB DE LA REINA SOCIAL DEPO</t>
+          <t>CORPORACION MUNICIPAL CLUB DE LA REINA SOCIAL DEPORTIVO Y RECREACIONAL</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Desarrollo Social de Coli</t>
+          <t>Corporación Municipal de Desarrollo Social de Colina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Administración de Fondos de Terceros</t>
+          <t>Comisión Chilena de Energía Nuclear</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Departamento Administrativo de Salud Municipal.</t>
+          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6165,7 +6165,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6282,7 +6282,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Academia Politécnica Naval</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6343,7 +6343,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Academia Politécnica Naval</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6648,7 +6648,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE FOMENTO AL DESARROLLO ECONOMICO Y PRODUCTIVO</t>
+          <t>Centro Ideactiva</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6770,7 +6770,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -7075,7 +7075,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Quillon - Educación</t>
+          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7746,12 +7746,12 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE RECOLETA</t>
+          <t>I MUNICIPALIDAD DE RECOLETA</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7990,7 +7990,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES Y ANTARTICA CHILENA</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8051,7 +8051,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Educación Municipal</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8417,7 +8417,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE VITACURA</t>
+          <t>I MUNICIPALIDAD DE VITACURA</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8539,7 +8539,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Desarrollo Social Lampa</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE LAMPA</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -9159,7 +9159,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TECNOIMPORT SPA</t>
+          <t>comercializadora TecnoImport SpA</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -9271,7 +9271,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>ESCUELA NAVAL "ARTURO PRAT"</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9403,7 +9403,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TECNOIMPORT SPA</t>
+          <t>comercializadora TecnoImport SpA</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -9454,7 +9454,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>COMISION CHILENA DE ENERGIA NUCLEAR</t>
+          <t>Comisión Chilena de Energía Nuclear</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9576,7 +9576,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>COMISION CHILENA DE ENERGIA NUCLEAR</t>
+          <t>Comisión Chilena de Energía Nuclear</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -10613,7 +10613,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>COMISION CHILENA DE ENERGIA NUCLEAR</t>
+          <t>Comisión Chilena de Energía Nuclear</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -10674,7 +10674,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>INSTITUTO GEOGRAFICO MILITAR</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>COMISION CHILENA DE ENERGIA NUCLEAR</t>
+          <t>Comisión Chilena de Energía Nuclear</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -11172,7 +11172,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TECNOIMPORT SPA</t>
+          <t>comercializadora TecnoImport SpA</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -11406,7 +11406,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE CERRO NAVIA</t>
+          <t>I.MUNICIPALIDAD DE CERRO NAVIA</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -11589,7 +11589,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Iluste Municipalidad de Huechuraba</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -11650,7 +11650,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Iluste Municipalidad de Huechuraba</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -11711,7 +11711,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Iluste Municipalidad de Huechuraba</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -11833,7 +11833,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Servicio Nacional del Patrimonio Cultural</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -12199,7 +12199,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Dirección de Telecomunicaciones e Informática de la Armada</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -13180,7 +13180,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -13297,7 +13297,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>IMunicipalidad de Molina</t>
+          <t xml:space="preserve">ILUSTRE MUNICIPALIDAD DE MOLINA </t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -14273,7 +14273,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TRAIGUEN</t>
+          <t>MUNICIPALIDAD DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -14456,7 +14456,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Departamento de Salud</t>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -14578,7 +14578,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Retiro</t>
+          <t>ILUSTRE MUNICIPALIDAD DE RETIRO</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -14700,7 +14700,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Retiro</t>
+          <t>ILUSTRE MUNICIPALIDAD DE RETIRO</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -14944,7 +14944,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Fresia - Salud</t>
+          <t>I MUNICIPALIDAD DE FRESIA</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -15066,7 +15066,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Valparaíso para el Desarrollo Social</t>
+          <t>CORP MUNICIPAL DE VALPARAISO PARA EL DESARROLLO SOCIAL</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -15432,7 +15432,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Dirección Nacional de Fronteras y Límites del Esta</t>
+          <t>Dirección Nacional de Fronteras y Límites del Estado</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -15564,7 +15564,7 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t xml:space="preserve">AURA XD SPA </t>
+          <t>AURA XD SPA</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
@@ -15859,7 +15859,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE CERRO NAVIA</t>
+          <t>I.MUNICIPALIDAD DE CERRO NAVIA</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -16042,7 +16042,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>IMunicipalidad de Molina</t>
+          <t xml:space="preserve">ILUSTRE MUNICIPALIDAD DE MOLINA </t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -16225,7 +16225,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad De Curanilahue - Educación</t>
+          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -16347,7 +16347,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Educación Municipal</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -16469,7 +16469,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENAFLOR</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -16535,7 +16535,7 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
@@ -16652,7 +16652,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE CERRO NAVIA</t>
+          <t>I.MUNICIPALIDAD DE CERRO NAVIA</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">

--- a/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/mar-2026.xlsx
+++ b/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/mar-2026.xlsx
@@ -562,7 +562,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +818,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +883,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +948,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1013,11 @@
           <t>77.137.827-7</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1139,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1204,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1330,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1395,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1460,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1525,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1590,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1655,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1720,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1785,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1850,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1915,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1980,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2045,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2110,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2175,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2240,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2305,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2370,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2435,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2500,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2565,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2630,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2756,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2821,11 @@
           <t>77.727.285-3</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2886,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2951,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +3016,11 @@
           <t>77.508.642-4</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3081,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3146,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3211,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3276,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3341,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3406,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3471,11 @@
           <t>76.128.275-1</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3494,7 +3662,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3555,7 +3727,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3616,7 +3792,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3677,7 +3857,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3799,7 +3983,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3860,7 +4048,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3921,7 +4113,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4043,7 +4239,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4104,7 +4304,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4165,7 +4369,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4226,7 +4434,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4348,7 +4560,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4409,7 +4625,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4470,7 +4690,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4531,7 +4755,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4592,7 +4820,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4653,7 +4885,11 @@
           <t>77.137.827-7</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4714,7 +4950,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4775,7 +5015,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4836,7 +5080,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4897,7 +5145,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4958,7 +5210,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5019,7 +5275,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5080,7 +5340,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5202,7 +5466,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5263,7 +5531,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5324,7 +5596,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5385,7 +5661,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5446,7 +5726,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5507,7 +5791,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5568,7 +5856,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5690,7 +5982,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5751,7 +6047,11 @@
           <t>77.137.827-7</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5873,7 +6173,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5995,7 +6299,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6056,7 +6364,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6117,7 +6429,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6178,7 +6494,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6239,7 +6559,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6300,7 +6624,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6422,7 +6750,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6483,7 +6815,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6544,7 +6880,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6849,7 +7189,11 @@
           <t>77.727.285-3</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6971,7 +7315,11 @@
           <t>77.727.285-3</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7032,7 +7380,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7093,7 +7445,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7154,7 +7510,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7215,7 +7575,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7276,7 +7640,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7337,7 +7705,11 @@
           <t>77.727.285-3</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7520,7 +7892,11 @@
           <t>76.128.275-1</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7581,7 +7957,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7642,7 +8022,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7703,7 +8087,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7764,7 +8152,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7825,7 +8217,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7886,7 +8282,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7947,7 +8347,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8130,7 +8534,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8191,7 +8599,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8313,7 +8725,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8374,7 +8790,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8435,7 +8855,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8496,7 +8920,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8557,7 +8985,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8618,7 +9050,11 @@
           <t>77.727.285-3</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8679,7 +9115,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8923,7 +9363,11 @@
           <t>77.727.285-3</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9045,7 +9489,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9106,7 +9554,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9167,7 +9619,11 @@
           <t>77.168.105-0</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9350,7 +9806,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9411,7 +9871,11 @@
           <t>77.168.105-0</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9472,7 +9936,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9533,7 +10001,11 @@
           <t>77.727.285-3</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9655,7 +10127,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9716,7 +10192,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9777,7 +10257,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9899,7 +10383,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9960,7 +10448,11 @@
           <t>77.727.285-3</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10082,7 +10574,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10143,7 +10639,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10204,7 +10704,11 @@
           <t>77.319.537-4</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10265,7 +10769,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10326,7 +10834,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10448,7 +10960,11 @@
           <t>77.727.285-3</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10509,7 +11025,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10631,7 +11151,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10692,7 +11216,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10814,7 +11342,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10875,7 +11407,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10997,7 +11533,11 @@
           <t>77.137.827-7</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11058,7 +11598,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11119,7 +11663,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11180,7 +11728,11 @@
           <t>77.168.105-0</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11241,7 +11793,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11363,7 +11919,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11546,7 +12106,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11607,7 +12171,11 @@
           <t>77.727.285-3</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11668,7 +12236,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11729,7 +12301,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11790,7 +12366,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11851,7 +12431,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11912,7 +12496,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12095,7 +12683,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12217,7 +12809,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12400,7 +12996,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12461,7 +13061,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12583,7 +13187,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12644,7 +13252,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12766,7 +13378,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12827,7 +13443,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12888,7 +13508,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12949,7 +13573,11 @@
           <t>77.137.827-7</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13254,7 +13882,11 @@
           <t>76.819.088-7</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13315,7 +13947,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13437,7 +14073,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13498,7 +14138,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13559,7 +14203,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13620,7 +14268,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13681,7 +14333,11 @@
           <t>77.137.827-7</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13803,7 +14459,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13925,7 +14585,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14047,7 +14711,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14108,7 +14776,11 @@
           <t>77.137.827-7</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14169,7 +14841,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14230,7 +14906,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14352,7 +15032,11 @@
           <t>76.872.717-1</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14413,7 +15097,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14474,7 +15162,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14535,7 +15227,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14596,7 +15292,11 @@
           <t>77.319.537-4</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14657,7 +15357,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14718,7 +15422,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14840,7 +15548,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14901,7 +15613,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14962,7 +15678,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15023,7 +15743,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15084,7 +15808,11 @@
           <t>76.819.088-7</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15145,7 +15873,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15206,7 +15938,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15267,7 +16003,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15328,7 +16068,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15389,7 +16133,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15633,7 +16381,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15694,7 +16446,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15877,7 +16633,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15938,7 +16698,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15999,7 +16763,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16121,7 +16889,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16243,7 +17015,11 @@
           <t>76.819.088-7</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16304,7 +17080,11 @@
           <t>77.727.285-3</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16426,7 +17206,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16487,7 +17271,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16548,7 +17336,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16609,7 +17401,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16731,7 +17527,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
